--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136828752</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828753</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136828754</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136828756</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136828759</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136828760</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136828761</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>136828762</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136828763</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136828765</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136828766</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136828767</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136828768</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136828769</v>
       </c>
       <c r="B17" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136828771</v>
       </c>
       <c r="B18" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>136828772</v>
       </c>
       <c r="B19" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>136828773</v>
       </c>
       <c r="B20" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136828774</v>
       </c>
       <c r="B21" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136828752</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828753</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136828754</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136828756</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136828759</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136828760</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136828761</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>136828762</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136828763</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136828765</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136828766</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136828767</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136828768</v>
       </c>
       <c r="B16" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136828769</v>
       </c>
       <c r="B17" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136828771</v>
       </c>
       <c r="B18" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>136828772</v>
       </c>
       <c r="B19" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>136828773</v>
       </c>
       <c r="B20" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136828774</v>
       </c>
       <c r="B21" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136828752</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828753</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136828754</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136828756</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136828759</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136828760</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136828761</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>136828762</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136828763</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136828765</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136828766</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136828767</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136828768</v>
       </c>
       <c r="B16" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136828769</v>
       </c>
       <c r="B17" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136828771</v>
       </c>
       <c r="B18" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>136828772</v>
       </c>
       <c r="B19" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>136828773</v>
       </c>
       <c r="B20" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136828774</v>
       </c>
       <c r="B21" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136828752</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828753</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136828754</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136828756</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136828759</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136828760</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136828761</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>136828762</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136828763</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136828765</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136828766</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136828767</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136828768</v>
       </c>
       <c r="B16" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136828769</v>
       </c>
       <c r="B17" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136828771</v>
       </c>
       <c r="B18" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>136828772</v>
       </c>
       <c r="B19" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>136828773</v>
       </c>
       <c r="B20" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136828774</v>
       </c>
       <c r="B21" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136828752</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828753</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136828754</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136828756</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136828759</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136828760</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136828761</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>136828762</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136828763</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136828765</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136828766</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136828767</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136828768</v>
       </c>
       <c r="B16" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136828769</v>
       </c>
       <c r="B17" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136828771</v>
       </c>
       <c r="B18" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>136828772</v>
       </c>
       <c r="B19" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>136828773</v>
       </c>
       <c r="B20" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136828774</v>
       </c>
       <c r="B21" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136828752</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828753</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136828754</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136828756</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136828759</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136828760</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136828761</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>136828762</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136828763</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136828765</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136828766</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136828767</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136828768</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136828769</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136828771</v>
       </c>
       <c r="B18" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>136828772</v>
       </c>
       <c r="B19" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>136828773</v>
       </c>
       <c r="B20" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136828774</v>
       </c>
       <c r="B21" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136828755</v>
       </c>
       <c r="B22" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136828752</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828753</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136828754</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136828756</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136828759</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136828760</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136828761</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>136828762</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136828763</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136828765</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136828766</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136828767</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136828768</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136828769</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136828771</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>136828772</v>
       </c>
       <c r="B19" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>136828773</v>
       </c>
       <c r="B20" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136828774</v>
       </c>
       <c r="B21" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136828755</v>
       </c>
       <c r="B22" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136828758</v>
       </c>
       <c r="B23" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>136828764</v>
       </c>
       <c r="B24" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -3079,11 +3079,7 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bjurvasslan, Dlr</t>
@@ -3196,11 +3192,7 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bjurvasslan, Dlr</t>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136828752</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828753</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136828754</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136828756</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136828759</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136828760</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136828761</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>136828762</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136828763</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136828765</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136828766</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136828767</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136828768</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136828769</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136828771</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>136828772</v>
       </c>
       <c r="B19" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>136828773</v>
       </c>
       <c r="B20" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136828774</v>
       </c>
       <c r="B21" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136828755</v>
       </c>
       <c r="B22" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136828758</v>
       </c>
       <c r="B23" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>136828764</v>
       </c>
       <c r="B24" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136828752</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828753</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136828754</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136828756</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136828759</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136828760</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136828761</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>136828762</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136828763</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136828765</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136828766</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136828767</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136828768</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136828769</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136828771</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>136828772</v>
       </c>
       <c r="B19" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>136828773</v>
       </c>
       <c r="B20" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136828774</v>
       </c>
       <c r="B21" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136828755</v>
       </c>
       <c r="B22" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136828752</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828753</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136828754</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136828756</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136828759</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136828760</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136828761</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>136828762</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136828763</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136828765</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136828766</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136828767</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136828768</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136828769</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136828771</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>136828772</v>
       </c>
       <c r="B19" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>136828773</v>
       </c>
       <c r="B20" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136828774</v>
       </c>
       <c r="B21" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136828755</v>
       </c>
       <c r="B22" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 37505-2026 artfynd.xlsx
+++ b/artfynd/A 37505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828757</v>
       </c>
       <c r="B2" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136828770</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136828752</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828753</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136828754</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136828756</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136828759</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>136828760</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136828761</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>136828762</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136828763</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>136828765</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136828766</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136828767</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136828768</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136828769</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>136828771</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>136828772</v>
       </c>
       <c r="B19" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>136828773</v>
       </c>
       <c r="B20" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136828774</v>
       </c>
       <c r="B21" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
